--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.12643884861977</v>
+        <v>12.69554631290071</v>
       </c>
       <c r="D2" t="n">
-        <v>67.02072647903614</v>
+        <v>10.89086805284337</v>
       </c>
       <c r="E2" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F2" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.60258211008774</v>
+        <v>11.47291959288926</v>
       </c>
       <c r="D3" t="n">
-        <v>69.31604758881956</v>
+        <v>11.26385773318318</v>
       </c>
       <c r="E3" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F3" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.13753583721284</v>
+        <v>8.959849573547087</v>
       </c>
       <c r="D4" t="n">
-        <v>42.25221887664599</v>
+        <v>6.865985567454974</v>
       </c>
       <c r="E4" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F4" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.07058344784701</v>
+        <v>8.948969810275139</v>
       </c>
       <c r="D5" t="n">
-        <v>49.84286010538068</v>
+        <v>8.099464767124362</v>
       </c>
       <c r="E5" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F5" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.00655691348216</v>
+        <v>6.988565498440851</v>
       </c>
       <c r="D6" t="n">
-        <v>27.57263135792448</v>
+        <v>4.480552595662727</v>
       </c>
       <c r="E6" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F6" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.03183993889495</v>
+        <v>5.04267399007043</v>
       </c>
       <c r="D7" t="n">
-        <v>19.08312167544447</v>
+        <v>3.101007272259727</v>
       </c>
       <c r="E7" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F7" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.56716854266732</v>
+        <v>5.779664888183441</v>
       </c>
       <c r="D8" t="n">
-        <v>11.92581471805354</v>
+        <v>1.937944891683701</v>
       </c>
       <c r="E8" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F8" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.90191255149557</v>
+        <v>4.534060789618031</v>
       </c>
       <c r="D9" t="n">
-        <v>16.98665609414551</v>
+        <v>2.760331615298646</v>
       </c>
       <c r="E9" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F9" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.59535095507568</v>
+        <v>5.134244530199799</v>
       </c>
       <c r="D10" t="n">
-        <v>19.98419159816576</v>
+        <v>3.247431134701937</v>
       </c>
       <c r="E10" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F10" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.81095541583521</v>
+        <v>5.169280255073223</v>
       </c>
       <c r="D11" t="n">
-        <v>21.01061779810502</v>
+        <v>3.414225392192066</v>
       </c>
       <c r="E11" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F11" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.24300780958625</v>
+        <v>7.514488769057766</v>
       </c>
       <c r="D12" t="n">
-        <v>24.83803569949263</v>
+        <v>4.036180801167553</v>
       </c>
       <c r="E12" t="n">
-        <v>16.18483458076334</v>
+        <v>2.630035619374044</v>
       </c>
       <c r="F12" t="n">
-        <v>19.41125425917621</v>
+        <v>3.154328817116134</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
